--- a/data/financieel.xlsx
+++ b/data/financieel.xlsx
@@ -944,7 +944,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ead3fa8a-6137-414e-a276-e9304495ab3a}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7afb9708-8388-49c7-af15-862714c73e6e}">
   <dimension ref="A1:N104"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>

--- a/data/financieel.xlsx
+++ b/data/financieel.xlsx
@@ -944,7 +944,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7afb9708-8388-49c7-af15-862714c73e6e}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{f09e8362-eac7-4283-ad28-340e027ce139}">
   <dimension ref="A1:N104"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>

--- a/data/financieel.xlsx
+++ b/data/financieel.xlsx
@@ -944,7 +944,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236ccadb-12a2-44f2-9b43-049584e89a46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0c00cf73-1d86-4851-b7a4-a7289b4648f9}">
   <dimension ref="A1:N104"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
